--- a/public/data/schools.xlsx
+++ b/public/data/schools.xlsx
@@ -1,29 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02dd4aa8eaaca434/Desktop/robotix/public/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_294391A7924BE2CFEF03481445E35E79C10DDEA6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3E32AC6-51FB-49F5-9D5F-10B3288D5E91}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Schools" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Schools" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Schools!$A$1:$D$6</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>schoolName</t>
   </si>
@@ -37,15 +25,15 @@
     <t>notes</t>
   </si>
   <si>
+    <t>Central Magnet Middle School</t>
+  </si>
+  <si>
+    <t>Rutherford County Schools</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Rutherford County Schools</t>
-  </si>
-  <si>
-    <t>Central Magnet Middle School</t>
-  </si>
-  <si>
     <t>Central Magnet High School</t>
   </si>
   <si>
@@ -53,22 +41,29 @@
   </si>
   <si>
     <t>Check with us for More Listed Schools</t>
+  </si>
+  <si>
+    <t>Blackman Middle School</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -103,7 +98,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -111,7 +106,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -198,6 +193,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -232,6 +228,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -266,20 +263,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -401,22 +394,62 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,19 +463,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -450,11 +483,11 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -462,30 +495,33 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" ht="29.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="D6" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:D6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/public/data/schools.xlsx
+++ b/public/data/schools.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>schoolName</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Check with us for More Listed Schools</t>
+  </si>
+  <si>
+    <t>Rutherford County Schools Only</t>
   </si>
   <si>
     <t>Blackman Middle School</t>
@@ -503,13 +506,17 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
